--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,328 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131796217</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136933204</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102705</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sågbergstäppan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>502342</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6685789</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933204</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136933205</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102705</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sågbergstäppan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>502346</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6685818</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933205</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136933206</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102705</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sågbergstäppan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>502341</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6685866</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933206</t>
         </is>
       </c>
     </row>
@@ -929,6 +1251,9 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136933204</v>
       </c>
       <c r="B4" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136933205</v>
       </c>
       <c r="B5" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136933206</v>
       </c>
       <c r="B6" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
